--- a/medford_videoprotsessory.xlsx
+++ b/medford_videoprotsessory.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессоры для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Pentax, Aohua, Olympus, Fujinon, GE — всего 20 позиций.</t>
+          <t>Видеопроцессоры для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Pentax, Aohua, Olympus, Fujinon, GE.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_videoprotsessory.xlsx
+++ b/medford_videoprotsessory.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать видеопроцессоры для клиники?</t>
+          <t>Как понять, подойдёт ли процессор к моим эндоскопам?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Разрешение изображения, Источник света, Страна производства, КТРУ). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Совместимость определяется платформой производителя и серией эндоскопов. В спецификации процессора указан список поддерживаемых серий: Pentax EPK-3000 DEFINA — серии Kp/70K/80K/90K/K10/J10 и фиброскопы с видеомодулем, Aohua AQ-200 — серии FHD-GT/CL. Эндоскоп другой марки, как правило, не заводится без штатной совместимости. Сверяйте по документации до покупки.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Чем отличается HD от Full HD?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>HD — это разрешение 1280×720 точек, Full HD — 1920×1080. Full HD даёт более детальное изображение и запас по чёткости при выводе на крупный монитор. В каталоге есть обе группы. Реальную детализацию ограничивает и матрица эндоскопа, поэтому разрешение процессора согласуют с возможностями всей связки.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Нужен ли отдельный источник света?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены SonoScape, Pentax, Aohua, Olympus, Fujinon, GE. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Зависит от модели. Часть процессоров имеет встроенный источник света (Pentax EPK-i5500c, EPK i7010), и дополнительный блок не требуется. Другие работают с отдельным блоком освещения (Olympus CV-290, SonoScape HD-550). Отдельный блок занимает больше места, но упрощает замену источника света независимо от процессора.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Какие интерфейсы вывода нужны?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Процессоры выводят изображение через HDMI, DVI или SDI. Например, HUGER VEP-2600F оснащён двумя выходами DVI. Тип и число интерфейсов подбирают под монитор и систему документирования отделения. Если разъёмы не совпадают, потребуются переходники, что может ограничить качество записи, поэтому интерфейсы проверяют заранее.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Можно ли подключить эндоскопы разных марок?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Штатно процессор работает с эндоскопами своей платформы. Некоторые решения допускают подключение через адаптеры, но набор функций при этом может сокращаться, а часть режимов визуализации становится недоступной. Возможность и последствия такого подключения уточняют у производителя; для стабильной работы предпочтительна единая платформа.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что такое видеокапсульная эндоскопия?</t>
+          <t>Что даёт технология NBI и подобные режимы?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Режимы узкоспектральной и виртуальной хромоэндоскопии усиливают контраст сосудистого рисунка и слизистой, помогая врачу оценивать структуру тканей. Набор доступных режимов зависит от модели процессора и совместимого эндоскопа. Конкретные технологии для вашей связки уточняйте по спецификации, а клиническую интерпретацию изображения выполняет врач.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Что такое эндоскопический метод операции?</t>
+          <t>Нужно ли регистрационное удостоверение?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Да. Видеопроцессор — медицинское изделие, и его вводят в оборот при наличии действующего регистрационного удостоверения Росздравнадзора на конкретную модель. Перед приобретением сверяют статус РУ, доступность обновлений программного обеспечения и условия сервисного обслуживания платформы у поставщика.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессоры для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Pentax, Aohua, Olympus, Fujinon, GE.</t>
+          <t>Видеопроцессор эндоскопический — блок, который принимает сигнал с матрицы эндоскопа, обрабатывает его и формирует изображение для монитора в реальном времени. В каталоге собраны процессоры Olympus, Pentax, Fujinon, SonoScape, Aohua и HUGER с разрешением HD (1280×720) и Full HD (1920×1080). Часть моделей имеет встроенный источник света (Pentax EPK-i5500c, EPK i7010), часть работает с отдельным блоком освещения (Olympus CV-290, SonoScape HD-550). Совместимость с эндоскопами привязана к платформе производителя — например, Pentax EPK-3000 DEFINA работает с сериями Kp/70K/80K/90K/K10/J10.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Классификация видеопроцессоров</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое видеопроцессоры</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4506,251 +4506,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Классификация видеопроцессоров</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Критерий</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Разрешение изображения</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Источник света</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Страна производства</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>КТРУ</t>
+          <t>Варианты</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессор SonoScape HD-500 (FullHD)</t>
+          <t>По разрешению</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SonoScape</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1920×1080 (Full HD)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Отдельный блок</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>HD 1280×720 / Full HD 1920×1080 / 4K и выше</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессор Pentax IMAGINA EPK-i5500c</t>
+          <t>По источнику света</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Pentax</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>1920×1080 (Full HD)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Встроенный</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>встроенный / отдельный блок</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессор Aohua AQ-200</t>
+          <t>По типу эндоскопов</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Aohua</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>для гибких / для жёстких</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессор Pentax EPK i5000</t>
+          <t>По функциональности</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Pentax</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>1920×1080 (Full HD)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Встроенный</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Видеопроцессор Aohua VME 2600 HD</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Aohua</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>26.60.12.119-00000376</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Видеопроцессор Olympus CV-170 (Optera)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Olympus</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>1920×1080 (Full HD)</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>многофункциональные / портативные / специализированные</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4762,7 +4594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5088,12 +4920,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите платформу эндоскопов</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается видеопроцессоры: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Видеопроцессор и эндоскопы образуют единую платформу одного производителя. Сначала уточняют, эндоскопы какой марки и серии уже есть в отделении: процессор Pentax рассчитан на эндоскопы Pentax (например, EPK-3000 DEFINA — серии Kp/70K/80K/90K/K10/J10), Aohua AQ-200 — на серии FHD-GT/CL. Совместимость первична, остальные параметры вторичны.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5133,12 +4965,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите разрешение</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>В каталоге представлены процессоры с разрешением HD (1280×720) и Full HD (1920×1080). Для диагностики важны высокое разрешение и точная цветопередача. Full HD дают Olympus CV-290, Pentax EPK-i5500c, Fujinon EPX-2500, SonoScape HD-550; HD — Olympus CV-190, SonoScape HD-350. Разрешение процессора согласуют с возможностями эндоскопа и монитора.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5178,12 +5010,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Учтите источник света</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Разрешение изображения, Источник света, Страна производства, КТРУ. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Часть процессоров имеет встроенный источник света (Pentax EPK-i5500c, EPK i7010 OPTIVISTA Plus), часть работает с отдельным блоком освещения (Olympus CV-290, SonoScape HD-550). Встроенный вариант компактнее и проще в размещении, отдельный блок даёт гибкость при замене. Выбор зависит от компоновки рабочего места и имеющегося оборудования.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5223,12 +5055,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Проверьте интерфейсы вывода</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: SonoScape, Pentax, Aohua, Olympus, Fujinon, GE.</t>
+          <t>Процессор подключается к монитору и периферии через HDMI, DVI или SDI — например, HUGER VEP-2600F имеет два выхода DVI. Число и тип интерфейсов сверяют с монитором, архиватором и системой документирования отделения. Нехватка нужного выхода означает переходники или ограничения при записи, поэтому разъёмы проверяют заранее.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5268,12 +5100,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Оцените функции визуализации и документирования</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Современные процессоры поддерживают технологии улучшения изображения и документирование: запись видео, стоп-кадр, интеграцию с архивом. Конкретный набор функций зависит от модели и платформы. Уточняйте по спецификации производителя, какие режимы визуализации доступны именно для вашей связки процессора и эндоскопов, а не по общему описанию категории.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5313,12 +5145,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните электропитание и регистрацию</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Проверяют параметры электропитания (например, HUGER VEP-2600F — 110–240 В, 50/60 Гц) и совместимость с сетью учреждения. Перед вводом в оборот сверяют наличие действующего регистрационного удостоверения Росздравнадзора на модель, доступность обновлений ПО и условия сервисной поддержки платформы.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5368,7 +5200,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессоры подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены SonoScape, Pentax, Aohua, Olympus, Fujinon, GE. При выборе обращают внимание на разрешение изображения, источник света, страна производства, ктру, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Видеопроцессор нельзя выбирать в отрыве от парка эндоскопов — это связка одной платформы. Первым делом сверяю, какие серии эндоскопов процессор поддерживает: Pentax EPK-3000 DEFINA работает с сериями Kp/70K/80K/90K/K10/J10, Aohua AQ-200 — с FHD-GT/CL. Дальше смотрю на разрешение и интерфейсы вывода под имеющийся монитор, а также встроен ли источник света или нужен отдельный блок. Разъёмы и версия ПО определяют, заведётся ли конкретный эндоскоп.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5652,13 +5484,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое видеопроцессоры</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Видеопроцессоры — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов SonoScape, Pentax, Aohua, Olympus, Fujinon, GE. Подберём вариант под задачи вашего отделения.</t>
+          <t>Видеопроцессор обрабатывает сигнал с сенсора эндоскопа и выводит изображение на монитор, а также управляет светом, ирригацией и аспирацией. В каталоге — модели Olympus, Pentax, Fujinon, SonoScape, Aohua, HUGER с разрешением HD или Full HD, со встроенным источником света или отдельным блоком. Главный критерий выбора — совместимость с эндоскопами вашей платформы: процессор Pentax рассчитан на эндоскопы Pentax, Aohua AQ-200 — на серии FHD-GT/CL. Дальше смотрят на разрешение, интерфейсы вывода и функции документирования.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5695,13 +5527,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое эндоскопический видеопроцессор</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Разрешение изображения, Источник света, Страна производства, КТРУ), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Видеопроцессор — центральный блок эндоскопической системы. Он принимает сигнал с CCD- или CMOS-сенсора эндоскопа, усиливает и корректирует его, формирует изображение на мониторе в реальном времени и управляет источником света, а также функциями ирригации и аспирации. От процессора зависят разрешение, цветопередача и доступные режимы визуализации.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5738,13 +5570,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Как выбрать видеопроцессор</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Главный критерий — совместимость с эндоскопами платформы. Процессор Pentax рассчитан на эндоскопы Pentax, Aohua AQ-200 — на серии FHD-GT/CL. Затем оценивают разрешение (HD или Full HD), наличие встроенного источника света, интерфейсы вывода и функции документирования. Все параметры согласуют с имеющимся парком эндоскопов и монитором отделения.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5781,13 +5613,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Виды видеопроцессоров</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Процессоры классифицируют по разрешению (HD, Full HD, 4K), источнику света (встроенный или отдельный блок), типу эндоскопов (для гибких или жёстких) и функциональности (многофункциональные, портативные, специализированные). В каталоге представлены модели Olympus, Pentax, Fujinon, SonoScape, Aohua и HUGER, охватывающие группы HD и Full HD.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5804,6 +5636,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Совместимость и интерфейсы</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Видеопроцессор подключается к монитору и периферии через HDMI, DVI или SDI; например, HUGER VEP-2600F имеет два выхода DVI. Перед покупкой сверяют разъёмы с оснащением, проверяют параметры электропитания и наличие регистрационного удостоверения. Стабильная работа связки процессор — эндоскоп — монитор обеспечивается единой платформой и совпадением интерфейсов.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>videoprotsessory</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
